--- a/excel-files/PASIG/PASIG CITY SCIENCE HS.xlsx
+++ b/excel-files/PASIG/PASIG CITY SCIENCE HS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C540A7A8-CD82-44B9-804E-C22D0710A50E}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F75094DD-3BFB-4EE4-B642-1DD0AFA7E60C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,15 +45,33 @@
   <commentList>
     <comment ref="E74" authorId="0" shapeId="0" xr:uid="{DF1E5537-8CCE-4DEB-8A35-90FA7F8FD90B}">
       <text>
-        <t xml:space="preserve">Unknown User:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Unknown User:
 Year Delivered 2022
 </t>
+        </r>
       </text>
     </comment>
     <comment ref="E89" authorId="0" shapeId="0" xr:uid="{F8B1E82A-A6C0-4941-B24B-6734FB7DBCA7}">
       <text>
-        <t>Unknown User:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Unknown User:
 Year delivered 2022</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -762,6 +780,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -773,12 +797,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5611,7 +5629,7 @@
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
     <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
@@ -5636,38 +5654,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5706,10 +5724,10 @@
       <c r="L2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>47</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5742,10 +5760,10 @@
       <c r="X2" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>59</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -13928,38 +13946,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13998,10 +14016,10 @@
       <c r="L2" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>73</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -14034,17 +14052,17 @@
       <c r="X2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>85</v>
       </c>
       <c r="AA2" s="26" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="30.75" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
